--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110313</v>
+        <v>110316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110316</v>
+        <v>110317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110317</v>
+        <v>110322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110322</v>
+        <v>110324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110324</v>
+        <v>110330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110330</v>
+        <v>110332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110332</v>
+        <v>110333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110339</v>
+        <v>110343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110343</v>
+        <v>110345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110345</v>
+        <v>110347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110347</v>
+        <v>110360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9360-2023 artfynd.xlsx
+++ b/artfynd/A 9360-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543994</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546927</v>
       </c>
       <c r="B3" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136542310</v>
       </c>
       <c r="B4" t="n">
-        <v>110360</v>
+        <v>110362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
